--- a/entertainment_forms/007_model_registration_form--entertainment_forms.xlsx
+++ b/entertainment_forms/007_model_registration_form--entertainment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'healthy',_'label':_'healthy'}</t>
+          <t>healthy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'healthy', 'label': 'Healthy'}</t>
+          <t>Healthy</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'sick',_'label':_'sick'}</t>
+          <t>sick</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'sick', 'label': 'Sick'}</t>
+          <t>Sick</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'dead',_'label':_'dead'}</t>
+          <t>dead</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'dead', 'label': 'Dead'}</t>
+          <t>Dead</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'30-34',_'label':_'30-34'}</t>
+          <t>30-34</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': '30-34', 'label': '30-34'}</t>
+          <t>30-34</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'35-39',_'label':_'35-39'}</t>
+          <t>35-39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': '35-39', 'label': '35-39'}</t>
+          <t>35-39</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'40-44',_'label':_'40-44'}</t>
+          <t>40-44</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': '40-44', 'label': '40-44'}</t>
+          <t>40-44</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'45-49',_'label':_'45-49'}</t>
+          <t>45-49</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': '45-49', 'label': '45-49'}</t>
+          <t>45-49</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'50-54',_'label':_'50-54'}</t>
+          <t>50-54</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': '50-54', 'label': '50-54'}</t>
+          <t>50-54</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'55-59',_'label':_'55-59'}</t>
+          <t>55-59</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': '55-59', 'label': '55-59'}</t>
+          <t>55-59</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'60-64',_'label':_'60-64'}</t>
+          <t>60-64</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': '60-64', 'label': '60-64'}</t>
+          <t>60-64</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'65-69',_'label':_'65-69'}</t>
+          <t>65-69</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': '65-69', 'label': '65-69'}</t>
+          <t>65-69</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'70-74',_'label':_'70-74'}</t>
+          <t>70-74</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': '70-74', 'label': '70-74'}</t>
+          <t>70-74</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'75-79',_'label':_'75-79'}</t>
+          <t>75-79</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': '75-79', 'label': '75-79'}</t>
+          <t>75-79</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'80-84',_'label':_'80-84'}</t>
+          <t>80-84</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': '80-84', 'label': '80-84'}</t>
+          <t>80-84</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'85-89',_'label':_'85-89'}</t>
+          <t>85-89</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': '85-89', 'label': '85-89'}</t>
+          <t>85-89</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'90-94',_'label':_'90-94'}</t>
+          <t>90-94</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': '90-94', 'label': '90-94'}</t>
+          <t>90-94</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'95-99',_'label':_'95-99'}</t>
+          <t>95-99</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': '95-99', 'label': '95-99'}</t>
+          <t>95-99</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'100+',_'label':_'100+'}</t>
+          <t>100+</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': '100+', 'label': '100+'}</t>
+          <t>100+</t>
         </is>
       </c>
     </row>
